--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.79632354000735</v>
+        <v>8.904402575251195</v>
       </c>
       <c r="D2" t="n">
-        <v>53.25817018835394</v>
+        <v>8.654452655607516</v>
       </c>
       <c r="E2" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F2" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.26285825111547</v>
+        <v>7.355214465806265</v>
       </c>
       <c r="D3" t="n">
-        <v>43.97796592900074</v>
+        <v>7.14641946346262</v>
       </c>
       <c r="E3" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F3" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>49.10968980161336</v>
+        <v>7.98032459276217</v>
       </c>
       <c r="D4" t="n">
-        <v>50.13063389578464</v>
+        <v>8.146228008065004</v>
       </c>
       <c r="E4" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F4" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.97596366964325</v>
+        <v>6.658594096317028</v>
       </c>
       <c r="D5" t="n">
-        <v>40.40438813188912</v>
+        <v>6.565713071431983</v>
       </c>
       <c r="E5" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F5" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>61.21177363010108</v>
+        <v>9.946913214891426</v>
       </c>
       <c r="D6" t="n">
-        <v>58.5121900085441</v>
+        <v>9.508230876388417</v>
       </c>
       <c r="E6" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F6" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.95387586855227</v>
+        <v>6.005004828639745</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77359911291226</v>
+        <v>5.975709855848242</v>
       </c>
       <c r="E7" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F7" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>50.64069644100631</v>
+        <v>8.229113171663526</v>
       </c>
       <c r="D8" t="n">
-        <v>47.92335615616565</v>
+        <v>7.787545375376919</v>
       </c>
       <c r="E8" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F8" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.14284546837649</v>
+        <v>5.710712388611181</v>
       </c>
       <c r="D9" t="n">
-        <v>33.53791714573037</v>
+        <v>5.449911536181185</v>
       </c>
       <c r="E9" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F9" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.66959775078929</v>
+        <v>7.096309634503259</v>
       </c>
       <c r="D10" t="n">
-        <v>41.16580793124456</v>
+        <v>6.689443788827241</v>
       </c>
       <c r="E10" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F10" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>28.68753514711841</v>
+        <v>4.661724461406743</v>
       </c>
       <c r="D11" t="n">
-        <v>26.21666578737442</v>
+        <v>4.260208190448343</v>
       </c>
       <c r="E11" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F11" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>30.14021614596641</v>
+        <v>4.897785123719542</v>
       </c>
       <c r="D12" t="n">
-        <v>27.25660603393918</v>
+        <v>4.429198480515117</v>
       </c>
       <c r="E12" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F12" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.76726804591415</v>
+        <v>2.72468105746105</v>
       </c>
       <c r="D13" t="n">
-        <v>18.69914959511055</v>
+        <v>3.038611809205465</v>
       </c>
       <c r="E13" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F13" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>45.76519397948511</v>
+        <v>7.436844021666331</v>
       </c>
       <c r="D14" t="n">
-        <v>42.767964945661</v>
+        <v>6.949794303669913</v>
       </c>
       <c r="E14" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F14" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>1.490292397587403</v>
+        <v>0.242172514607953</v>
       </c>
       <c r="D15" t="n">
-        <v>2.029152554412785</v>
+        <v>0.3297372900920776</v>
       </c>
       <c r="E15" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F15" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.00360051363529</v>
+        <v>3.250585083465734</v>
       </c>
       <c r="D16" t="n">
-        <v>21.89700568803321</v>
+        <v>3.558263424305396</v>
       </c>
       <c r="E16" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F16" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>49.22979043189035</v>
+        <v>7.999840945182182</v>
       </c>
       <c r="D17" t="n">
-        <v>50.5633705157861</v>
+        <v>8.216547708815241</v>
       </c>
       <c r="E17" t="n">
-        <v>15.10271540302344</v>
+        <v>2.454191252991309</v>
       </c>
       <c r="F17" t="n">
-        <v>14.40992046832832</v>
+        <v>2.341612076103352</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
